--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -33676,6 +33676,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1449">
+      <c r="A1449" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C1449" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G1449" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -33699,6 +33699,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>13200</v>
+      </c>
+      <c r="C1450" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -33722,6 +33722,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1451">
+      <c r="A1451" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>6200</v>
+      </c>
+      <c r="C1451" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -33745,6 +33745,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1452">
+      <c r="A1452" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C1452" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -33586,22 +33586,22 @@
     </row>
     <row r="1445">
       <c r="A1445" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1445" t="n">
-        <v>12000</v>
+        <v>3800</v>
       </c>
       <c r="C1445" t="n">
-        <v>1.51999998092651</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="D1445" t="n">
-        <v>1.45000004768372</v>
+        <v>1.44000005722046</v>
       </c>
       <c r="E1445" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="F1445" t="n">
         <v>1.46000003814697</v>
-      </c>
-      <c r="F1445" t="n">
-        <v>1.51999998092651</v>
       </c>
       <c r="G1445" t="s">
         <v>7</v>
@@ -33609,19 +33609,19 @@
     </row>
     <row r="1446">
       <c r="A1446" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1446" t="n">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="C1446" t="n">
-        <v>1.58000004291534</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="D1446" t="n">
-        <v>1.51999998092651</v>
+        <v>1.45000004768372</v>
       </c>
       <c r="E1446" t="n">
-        <v>1.58000004291534</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="F1446" t="n">
         <v>1.51999998092651</v>
@@ -33632,19 +33632,19 @@
     </row>
     <row r="1447">
       <c r="A1447" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1447" t="n">
-        <v>1400</v>
+        <v>3000</v>
       </c>
       <c r="C1447" t="n">
-        <v>1.51999998092651</v>
+        <v>1.58000004291534</v>
       </c>
       <c r="D1447" t="n">
         <v>1.51999998092651</v>
       </c>
       <c r="E1447" t="n">
-        <v>1.51999998092651</v>
+        <v>1.58000004291534</v>
       </c>
       <c r="F1447" t="n">
         <v>1.51999998092651</v>
@@ -33655,22 +33655,22 @@
     </row>
     <row r="1448">
       <c r="A1448" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1448" t="n">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="C1448" t="n">
-        <v>1.46000003814697</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="D1448" t="n">
-        <v>1.46000003814697</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="E1448" t="n">
-        <v>1.46000003814697</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="F1448" t="n">
-        <v>1.46000003814697</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="G1448" t="s">
         <v>7</v>
@@ -33678,22 +33678,22 @@
     </row>
     <row r="1449">
       <c r="A1449" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1449" t="n">
-        <v>22000</v>
+        <v>1000</v>
       </c>
       <c r="C1449" t="n">
-        <v>1.63999998569489</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="D1449" t="n">
-        <v>1.51999998092651</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="E1449" t="n">
-        <v>1.51999998092651</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="F1449" t="n">
-        <v>1.63999998569489</v>
+        <v>1.46000003814697</v>
       </c>
       <c r="G1449" t="s">
         <v>7</v>
@@ -33701,22 +33701,22 @@
     </row>
     <row r="1450">
       <c r="A1450" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1450" t="n">
-        <v>13200</v>
+        <v>22000</v>
       </c>
       <c r="C1450" t="n">
-        <v>1.79999995231628</v>
+        <v>1.63999998569489</v>
       </c>
       <c r="D1450" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F1450" t="n">
         <v>1.63999998569489</v>
-      </c>
-      <c r="E1450" t="n">
-        <v>1.63999998569489</v>
-      </c>
-      <c r="F1450" t="n">
-        <v>1.78999996185303</v>
       </c>
       <c r="G1450" t="s">
         <v>7</v>
@@ -33724,19 +33724,19 @@
     </row>
     <row r="1451">
       <c r="A1451" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1451" t="n">
-        <v>6200</v>
+        <v>13200</v>
       </c>
       <c r="C1451" t="n">
-        <v>1.78999996185303</v>
+        <v>1.79999995231628</v>
       </c>
       <c r="D1451" t="n">
-        <v>1.75</v>
+        <v>1.63999998569489</v>
       </c>
       <c r="E1451" t="n">
-        <v>1.78999996185303</v>
+        <v>1.63999998569489</v>
       </c>
       <c r="F1451" t="n">
         <v>1.78999996185303</v>
@@ -33747,16 +33747,16 @@
     </row>
     <row r="1452">
       <c r="A1452" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1452" t="n">
-        <v>1200</v>
+        <v>6200</v>
       </c>
       <c r="C1452" t="n">
         <v>1.78999996185303</v>
       </c>
       <c r="D1452" t="n">
-        <v>1.78999996185303</v>
+        <v>1.75</v>
       </c>
       <c r="E1452" t="n">
         <v>1.78999996185303</v>
@@ -33765,6 +33765,29 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1452" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>14200</v>
+      </c>
+      <c r="C1453" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>1.78999996185303</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="G1453" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -38205,6 +38205,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1456">
+      <c r="A1456" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>22800</v>
+      </c>
+      <c r="C1456" t="n">
+        <v>1.87999999523163</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="H1456" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -38231,6 +38231,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>1.76999998092651</v>
+      </c>
+      <c r="H1457" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -38242,7 +38242,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="D1457" t="n">
-        <v>1.79999995231628</v>
+        <v>1.76999998092651</v>
       </c>
       <c r="E1457" t="n">
         <v>1.79999995231628</v>
@@ -38254,6 +38254,32 @@
         <v>1.76999998092651</v>
       </c>
       <c r="H1457" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="H1458" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -38283,6 +38283,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="H1459" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -38361,6 +38361,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>7400</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="H1462" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -34044,6 +34044,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1465">
+      <c r="A1465" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1465" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G1465" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>4400</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F1466"/>
+      <c r="G1466" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -34083,8 +34083,31 @@
       <c r="E1466" t="n">
         <v>1.60000002384186</v>
       </c>
-      <c r="F1466"/>
+      <c r="F1466" t="n">
+        <v>1.70000004768372</v>
+      </c>
       <c r="G1466" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F1467"/>
+      <c r="G1467" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -34106,8 +34106,31 @@
       <c r="E1467" t="n">
         <v>1.75</v>
       </c>
-      <c r="F1467"/>
+      <c r="F1467" t="n">
+        <v>1.75</v>
+      </c>
       <c r="G1467" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>12400</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="F1468"/>
+      <c r="G1468" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -34129,8 +34129,31 @@
       <c r="E1468" t="n">
         <v>1.79999995231628</v>
       </c>
-      <c r="F1468"/>
+      <c r="F1468" t="n">
+        <v>1.83000004291534</v>
+      </c>
       <c r="G1468" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1469" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="F1469"/>
+      <c r="G1469" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -34159,6 +34159,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>1.87000000476837</v>
+      </c>
+      <c r="G1470" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -43124,6 +43124,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1475">
+      <c r="A1475" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1475" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="G1475" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="H1475" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1475" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1476" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I1476" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -43182,6 +43182,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1477">
+      <c r="A1477" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1477" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1477" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1477" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1478" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1478" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>4200</v>
+      </c>
+      <c r="I1478" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -43240,6 +43240,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1479">
+      <c r="A1479" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1479" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1479" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1479" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -43269,6 +43269,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1480">
+      <c r="A1480" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1480" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1480" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1480" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -43298,6 +43298,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1481">
+      <c r="A1481" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1481" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1481" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1482" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1482" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I1482" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MTS.MI.xlsx
+++ b/data/MTS.MI.xlsx
@@ -43356,6 +43356,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1483">
+      <c r="A1483" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1483" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1483" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>1.69000005722046</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>4600</v>
+      </c>
+      <c r="I1483" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
